--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18821,7 +18839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18903,6 +18921,122 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1965_66_0136 'Slovan Lysá n. L.' prev→CLUB_S1964_65_0196 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1965_66_0560 'Baník Doubrava-Kopaniny' prev→CLUB_S1964_65_0585 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1965_66_0451 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1965_66_0459 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0013</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1965_66_0013 'KVAL  skupina A' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0014</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1965_66_0014 'KVAL  skupina B' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0015</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1965_66_0015 'KVAL  skupina C' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0016</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1965_66_0016 'KVAL  skupina D' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -57239,6 +57373,237 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0136</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0136 'Slovan Lysá n. L.' prev→CLUB_S1964_65_0196 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0560</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0560 'Baník Doubrava-Kopaniny' prev→CLUB_S1964_65_0585 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0451</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0451 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0459</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0459 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0013</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1965_66_0013 'KVAL  skupina A' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0014</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1965_66_0014 'KVAL  skupina B' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0015</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1965_66_0015 'KVAL  skupina C' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0016</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1965_66_0016 'KVAL  skupina D' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9657,6 +9657,11 @@
           <t>CLUB_S1964_65_0543</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>TR_S1965_66_00347</t>
@@ -10517,6 +10522,11 @@
       <c r="R18" t="inlineStr">
         <is>
           <t>CLUB_S1964_65_0543</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -18839,7 +18849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18927,7 +18937,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1965_66_0136 'Slovan Lysá n. L.' prev→CLUB_S1964_65_0196 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18939,7 +18949,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1965_66_0560 'Baník Doubrava-Kopaniny' prev→CLUB_S1964_65_0585 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18951,7 +18961,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1965_66_0451 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18963,7 +18973,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1965_66_0459 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18973,14 +18983,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1965_66_0013</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1965_66_0013 'KVAL  skupina A' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0157 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18990,14 +18995,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S1965_66_0014</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1965_66_0014 'KVAL  skupina B' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0196 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19007,14 +19007,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NODE_S1965_66_0015</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1965_66_0015 'KVAL  skupina C' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19024,17 +19019,180 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NODE_S1965_66_0016</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1965_66_0016 'KVAL  skupina D' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0585 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -26660,12 +26818,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -27626,12 +27784,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -28488,12 +28646,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -31829,12 +31987,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Kladno = TJ Svazarm Autoškola Kladno (Wiki D42 - registr ustavy 04/2026). **Svazarm** = Svaz pro spolupraci s armadou (vojensko-sportovni organizace). Autoskola Kladno = paralelni klub. city Kladno.</t>
+          <t>Kladno = TJ Svazarm Autoškola Kladno (Wiki D42 - registr ustavy 04/2026). **Svazarm** = Svaz pro spolupraci s armadou (vojensko-sportovni organizace). Autoskola Kladno = paralelni klub. city Kladno. || TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Svazarm Autoškola Kladno</t>
+          <t>Kladno</t>
         </is>
       </c>
     </row>
@@ -35068,12 +35226,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -36238,12 +36396,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -40895,12 +41053,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -42385,12 +42543,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -44272,12 +44430,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Rychnov u Jablonce nad Nisou (Wiki D42 - registr ustavy 04/2026). POZOR: NE Rychnov nad Kněžnou (Královehradecký kraj!). Rychnov u Jablonce nN = Liberecky kraj. D. Rychnov = Dolni Rychnov u Sokolova (=Falknovske doly Sokolov!) city Rychnov.</t>
+          <t>Rychnov u Jablonce nad Nisou (Wiki D42 - registr ustavy 04/2026). POZOR: NE Rychnov nad Kněžnou (Královehradecký kraj!). Rychnov u Jablonce nN = Liberecky kraj. D. Rychnov = Dolni Rychnov u Sokolova (=Falknovske doly Sokolov!) city Rychnov. || TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Rychnov</t>
+          <t>Rychnov nad Kněžnou</t>
         </is>
       </c>
     </row>
@@ -48860,12 +49018,12 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Orlová = TJ Banik Důl Zápotocký Orlová (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Důl Zápotocký** = OKD důl pojmenovany po Antoninu Zapotockem. city Orlová.</t>
+          <t>Orlová = TJ Banik Důl Zápotocký Orlová (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Důl Zápotocký** = OKD důl pojmenovany po Antoninu Zapotockem. city Orlová. || TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>Důl Zápotocký Orlová</t>
+          <t>Orlová</t>
         </is>
       </c>
     </row>
@@ -49705,12 +49863,12 @@
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>Orlová = TJ Banik Důl Zápotocký Orlová (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Důl Zápotocký** = OKD důl pojmenovany po Antoninu Zapotockem. city Orlová.</t>
+          <t>Orlová = TJ Banik Důl Zápotocký Orlová (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Důl Zápotocký** = OKD důl pojmenovany po Antoninu Zapotockem. city Orlová. || TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>Důl Zápotocký Orlová</t>
+          <t>Orlová</t>
         </is>
       </c>
     </row>
@@ -52557,12 +52715,12 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>Ústí = TJ Sokol Ústí (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Usti v CR - Usti nad Labem (Severocesky), Usti nad Orlici (Vychodocesky), Usti u Vsetina (Zlinsky/Severomoravsky). K overeni. city Ústí.</t>
+          <t>Ústí = TJ Sokol Ústí (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Usti v CR - Usti nad Labem (Severocesky), Usti nad Orlici (Vychodocesky), Usti u Vsetina (Zlinsky/Severomoravsky). K overeni. city Ústí. || TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>Ústí</t>
+          <t>Ústí u Vsetína</t>
         </is>
       </c>
     </row>
@@ -52940,12 +53098,12 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -57379,11 +57537,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -57428,21 +57586,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0136</t>
+          <t>CLUB_S1965_66_0022</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0136 'Slovan Lysá n. L.' prev→CLUB_S1964_65_0196 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -57450,21 +57606,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0560</t>
+          <t>CLUB_S1965_66_0049</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0560 'Baník Doubrava-Kopaniny' prev→CLUB_S1964_65_0585 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -57472,21 +57626,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0451</t>
+          <t>CLUB_S1965_66_0074</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0451 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -57494,21 +57646,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0459</t>
+          <t>CLUB_S1965_66_0129</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0459 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -57516,21 +57666,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1965_66_0013</t>
+          <t>CLUB_S1965_66_0131</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1965_66_0013 'KVAL  skupina A' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0157 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -57538,21 +57686,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S1965_66_0014</t>
+          <t>CLUB_S1965_66_0136</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1965_66_0014 'KVAL  skupina B' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0196 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -57560,21 +57706,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S1965_66_0015</t>
+          <t>CLUB_S1965_66_0147</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1965_66_0015 'KVAL  skupina C' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -57582,24 +57726,302 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NODE_S1965_66_0016</t>
+          <t>CLUB_S1965_66_0219</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1965_66_0016 'KVAL  skupina D' (L25, parent=NODE_S1965_66_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0244</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0349</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0350</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0383</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0385</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0419</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0426</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0430</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0491</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0530</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0550</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0560</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0585 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0611</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1965_66_0620</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18849,7 +18849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18937,7 +18937,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18949,7 +18949,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18961,7 +18961,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0157 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18973,7 +18973,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0196 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18985,7 +18985,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0157 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18997,7 +18997,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0196 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19009,7 +19009,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19021,7 +19021,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19033,7 +19033,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19045,7 +19045,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19057,7 +19057,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19069,7 +19069,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19081,7 +19081,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19093,7 +19093,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19105,94 +19105,10 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0585 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0585 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19209,7 +19125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19268,6 +19184,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19310,6 +19231,11 @@
           <t>10 týmů, jeden stůl (poprvé redukovaná liga). Mistr: ZKL Brno. Sestup: Spartak Plzeň.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19357,6 +19283,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19399,6 +19330,11 @@
           <t>3 skupiny (A,B,C) + SNHL (Slovensko). Čtyřkolově. Kvalifikace o I.ligu na konci. Poslední týmy sk. A-D sestoupily přímo; předposlední týmy sk. A-C hrály o udržení v kvalifikaci o 2.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19441,6 +19377,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19483,6 +19424,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19525,6 +19471,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19567,6 +19518,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19609,6 +19565,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19651,6 +19612,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19693,6 +19659,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19782,6 +19753,11 @@
           <t>Kvalifikace o postup do II.ligy. Motorlet B nemohl postoupit, proto postoupila Dukla Písek. Dvůr Králové n/L nenastoupil a všechna utkání byla kontumována 0:5. Havířov-Suchá po 3. kole odstoupil, neodehraná utkání byla kontumována 0:5. V kvalifikaci chybí výsledky třetin.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0011</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19824,6 +19800,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0012</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19866,6 +19847,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0013</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19908,6 +19894,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0014</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19950,6 +19941,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0015</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19992,6 +19988,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0016</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20286,6 +20287,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0020</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20328,6 +20334,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0021</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -20370,6 +20381,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0022</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20412,6 +20428,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0023</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -20454,6 +20475,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0024</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -20496,6 +20522,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -20538,6 +20569,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0026</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -20580,6 +20616,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0027</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -21047,6 +21088,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0033</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -21089,6 +21135,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0034</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -21131,6 +21182,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0035</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -21304,6 +21360,11 @@
           <t>Kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0038</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -21346,6 +21407,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0039</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -21687,6 +21753,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0047</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -21771,6 +21842,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0051</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21813,6 +21889,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0052</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -21855,6 +21936,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0053</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -21897,6 +21983,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0054</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -21939,6 +22030,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0055</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -21981,6 +22077,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0056</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -22023,6 +22124,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0057</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22065,6 +22171,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0058</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -22107,6 +22218,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0059</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -22327,6 +22443,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0058</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -22369,6 +22490,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0060</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -22411,6 +22537,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0061</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -22453,6 +22584,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0062</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -22495,6 +22631,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0063</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -22579,6 +22720,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0065</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -22621,6 +22767,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0066</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -22663,6 +22814,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0067</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -22705,6 +22861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0068</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -22752,6 +22913,11 @@
           <t>o postup do krajského přeboru</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0069</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -22799,6 +22965,11 @@
           <t>Kvalifikace o KS</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0070</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -22841,6 +23012,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0071</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -22925,6 +23101,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0073</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -23518,6 +23699,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0082</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -23560,6 +23746,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0083</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -24111,6 +24302,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0096</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -24148,6 +24344,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0097</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -24183,6 +24384,11 @@
       <c r="J117" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0100</t>
         </is>
       </c>
     </row>
@@ -26818,12 +27024,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -27784,12 +27990,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -41053,12 +41259,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -42543,12 +42749,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -44430,12 +44636,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Rychnov u Jablonce nad Nisou (Wiki D42 - registr ustavy 04/2026). POZOR: NE Rychnov nad Kněžnou (Královehradecký kraj!). Rychnov u Jablonce nN = Liberecky kraj. D. Rychnov = Dolni Rychnov u Sokolova (=Falknovske doly Sokolov!) city Rychnov. || TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rychnov u Jablonce nad Nisou (Wiki D42 - registr ustavy 04/2026). POZOR: NE Rychnov nad Kněžnou (Královehradecký kraj!). Rychnov u Jablonce nN = Liberecky kraj. D. Rychnov = Dolni Rychnov u Sokolova (=Falknovske doly Sokolov!) city Rychnov.</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Rychnov nad Kněžnou</t>
+          <t>Rychnov</t>
         </is>
       </c>
     </row>
@@ -52715,12 +52921,12 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>Ústí = TJ Sokol Ústí (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Usti v CR - Usti nad Labem (Severocesky), Usti nad Orlici (Vychodocesky), Usti u Vsetina (Zlinsky/Severomoravsky). K overeni. city Ústí. || TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Ústí = TJ Sokol Ústí (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Usti v CR - Usti nad Labem (Severocesky), Usti nad Orlici (Vychodocesky), Usti u Vsetina (Zlinsky/Severomoravsky). K overeni. city Ústí.</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>Ústí u Vsetína</t>
+          <t>Ústí</t>
         </is>
       </c>
     </row>
@@ -53098,12 +53304,12 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -57537,7 +57743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57591,12 +57797,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0022</t>
+          <t>CLUB_S1965_66_0074</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57611,12 +57817,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0049</t>
+          <t>CLUB_S1965_66_0129</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57631,12 +57837,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0074</t>
+          <t>CLUB_S1965_66_0131</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0157 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57651,12 +57857,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0129</t>
+          <t>CLUB_S1965_66_0136</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0196 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57671,12 +57877,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0131</t>
+          <t>CLUB_S1965_66_0147</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0157 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57691,12 +57897,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0136</t>
+          <t>CLUB_S1965_66_0219</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0196 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57711,12 +57917,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0147</t>
+          <t>CLUB_S1965_66_0244</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57731,12 +57937,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0219</t>
+          <t>CLUB_S1965_66_0349</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -57751,12 +57957,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0244</t>
+          <t>CLUB_S1965_66_0383</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57771,12 +57977,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0349</t>
+          <t>CLUB_S1965_66_0419</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57791,12 +57997,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0350</t>
+          <t>CLUB_S1965_66_0430</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57811,12 +58017,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0383</t>
+          <t>CLUB_S1965_66_0491</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57831,12 +58037,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0385</t>
+          <t>CLUB_S1965_66_0530</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57851,12 +58057,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0419</t>
+          <t>CLUB_S1965_66_0550</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57871,157 +58077,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1965_66_0426</t>
+          <t>CLUB_S1965_66_0560</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CLUB_S1965_66_0430</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CLUB_S1965_66_0491</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CLUB_S1965_66_0530</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CLUB_S1965_66_0550</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CLUB_S1965_66_0560</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0585 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S1965_66_0611</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S1965_66_0620</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Praha' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F23"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M10" t="n">
         <v>26</v>

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -55529,7 +55529,7 @@
         <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M9" t="n">
         <v>15</v>

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -19125,7 +19125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19187,6 +19187,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -19471,6 +19471,16 @@
           <t>NODE_S1965_66_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19485,6 +19495,14 @@
         <is>
           <t>NODE_S1964_65_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -19518,6 +19536,8 @@
           <t>NODE_S1965_66_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19532,6 +19552,14 @@
         <is>
           <t>NODE_S1964_65_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -19565,6 +19593,8 @@
           <t>NODE_S1965_66_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19579,6 +19609,14 @@
         <is>
           <t>NODE_S1964_65_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -20203,6 +20241,12 @@
           <t>NODE_S1965_66_0019</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20212,6 +20256,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -20245,6 +20297,8 @@
           <t>NODE_S1965_66_0019</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20254,6 +20308,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -20475,6 +20537,8 @@
           <t>NODE_S1965_66_0024</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20489,6 +20553,14 @@
         <is>
           <t>NODE_S1964_65_0024</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -21046,6 +21118,8 @@
           <t>NODE_S1965_66_0024</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21055,6 +21129,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -21580,6 +21662,8 @@
           <t>NODE_S1965_66_0049</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21589,6 +21673,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -21800,6 +21892,8 @@
           <t>NODE_S1965_66_0050</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21809,6 +21903,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -22030,6 +22132,8 @@
           <t>NODE_S1965_66_0059</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22044,6 +22148,14 @@
         <is>
           <t>NODE_S1964_65_0055</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -22678,6 +22790,8 @@
           <t>NODE_S1965_66_0073</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22687,6 +22801,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -23190,6 +23312,8 @@
           <t>NODE_S1965_66_0084</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23199,6 +23323,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -23316,6 +23448,8 @@
           <t>NODE_S1965_66_0084</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23325,6 +23459,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -23358,6 +23500,8 @@
           <t>NODE_S1965_66_0084</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23367,6 +23511,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -24223,6 +24375,8 @@
           <t>NODE_S1965_66_0101</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24232,6 +24386,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="114">
@@ -24265,6 +24427,8 @@
           <t>NODE_S1965_66_0101</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24274,6 +24438,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="115">

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -714,6 +714,11 @@
           <t>ZKL Brno</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
@@ -19536,8 +19541,6 @@
           <t>NODE_S1965_66_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19593,8 +19596,6 @@
           <t>NODE_S1965_66_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20246,7 +20247,6 @@
           <t>NODE_S1965_66_0023</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20297,8 +20297,6 @@
           <t>NODE_S1965_66_0019</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20537,8 +20535,6 @@
           <t>NODE_S1965_66_0024</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21118,8 +21114,6 @@
           <t>NODE_S1965_66_0024</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21662,8 +21656,6 @@
           <t>NODE_S1965_66_0049</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21892,8 +21884,6 @@
           <t>NODE_S1965_66_0050</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22132,8 +22122,6 @@
           <t>NODE_S1965_66_0059</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22790,8 +22778,6 @@
           <t>NODE_S1965_66_0073</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23312,8 +23298,6 @@
           <t>NODE_S1965_66_0084</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23448,8 +23432,6 @@
           <t>NODE_S1965_66_0084</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23500,8 +23482,6 @@
           <t>NODE_S1965_66_0084</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24375,8 +24355,6 @@
           <t>NODE_S1965_66_0101</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24427,8 +24405,6 @@
           <t>NODE_S1965_66_0101</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -54846,7 +54822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55050,6 +55026,18 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>Motorlet B nemohl postoupit, proto postoupila Dukla Písek. V severočeské větvi šlo po odmítnutí Chomutova B do kvalifikace Ústí nad Labem. Ve středoslovenské větvi šla místo Banské Bystrice B do kvalifikace Dubnica nad Váhom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ZKL Brno</t>
         </is>
       </c>
     </row>

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -58930,7 +58930,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
@@ -59023,13 +59023,13 @@
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>19</v>

--- a/data/S1965_66_FINAL.xlsx
+++ b/data/S1965_66_FINAL.xlsx
@@ -38,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +57,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +89,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -98,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +119,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -57913,7 +57924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57970,7 +57981,7 @@
           <t>CLUB_S1965_66_0074</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57990,7 +58001,7 @@
           <t>CLUB_S1965_66_0129</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -58010,7 +58021,7 @@
           <t>CLUB_S1965_66_0131</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0157 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -58030,7 +58041,7 @@
           <t>CLUB_S1965_66_0136</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0196 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -58050,7 +58061,7 @@
           <t>CLUB_S1965_66_0147</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -58070,7 +58081,7 @@
           <t>CLUB_S1965_66_0219</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -58090,7 +58101,7 @@
           <t>CLUB_S1965_66_0244</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -58110,7 +58121,7 @@
           <t>CLUB_S1965_66_0349</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -58130,7 +58141,7 @@
           <t>CLUB_S1965_66_0383</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -58150,7 +58161,7 @@
           <t>CLUB_S1965_66_0419</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0665 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -58170,7 +58181,7 @@
           <t>CLUB_S1965_66_0430</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -58190,7 +58201,7 @@
           <t>CLUB_S1965_66_0491</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -58210,7 +58221,7 @@
           <t>CLUB_S1965_66_0530</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -58230,7 +58241,7 @@
           <t>CLUB_S1965_66_0550</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -58250,11 +58261,115 @@
           <t>CLUB_S1965_66_0560</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1964_65_0585 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>30_Východočeský L30 finále (východní Čechy) · NODE_S1965_66_0077</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Slavia VŠ rozpustila po sezóně mužstvo a hráči přešli, do Slovanu Přelouč), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L30 1.kolo · NODE_S1965_66_0069</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Spartak Smržovka - Jiskra Kamenický Šenov), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L30 2.kolo · NODE_S1965_66_0070</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Spartak Smržovka - Jiskra Jablonec nad Nisou), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>30_Jihomoravský L40 skupina B (Jihomoravský kraj) · NODE_S1965_66_0099</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Železárny Prostějov B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F16"/>
